--- a/游戏设计王/老虎机数学入门-PartV-触发率计算器.xlsx
+++ b/游戏设计王/老虎机数学入门-PartV-触发率计算器.xlsx
@@ -706,13 +706,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -1430,7 +1431,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1535,6 +1536,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5223,23 +5231,23 @@
       <c r="A6" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="52">
         <f>3*B4/B5</f>
         <v>0.15</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="52">
         <f>3*C4/C5</f>
         <v>0.15</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="52">
         <f>3*D4/D5</f>
         <v>0.15</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="52">
         <f>3*E4/E5</f>
         <v>0.15</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="52">
         <f>3*F4/F5</f>
         <v>0.15</v>
       </c>
@@ -5311,7 +5319,7 @@
       <c r="B10" s="6">
         <v>10</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="52">
         <f>COMBIN(5,3)*POWER(AVERAGE($B$6:$F$6),3)*POWER(1-AVERAGE($B$6:$F$6),5-3)</f>
         <v>0.024384375</v>
       </c>
@@ -5332,7 +5340,7 @@
       <c r="B11" s="6">
         <v>5</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="52">
         <f>COMBIN(5,4)*POWER(AVERAGE($B$6:$F$6),4)*POWER(1-AVERAGE($B$6:$F$6),5-4)</f>
         <v>0.0021515625</v>
       </c>
@@ -5353,7 +5361,7 @@
       <c r="B12" s="6">
         <v>1</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="52">
         <f>COMBIN(5,5)*POWER(AVERAGE($B$6:$F$6),5)*POWER(1-AVERAGE($B$6:$F$6),5-5)</f>
         <v>7.59375e-5</v>
       </c>
@@ -5394,7 +5402,7 @@
       <c r="B14" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="53">
         <f>SUM(C10:C12)</f>
         <v>0.026611875</v>
       </c>
@@ -5779,7 +5787,7 @@
       <c r="A33" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="53">
         <f>1-POISSON($B$29-1,$B$32,TRUE())</f>
         <v>0.758563549029724</v>
       </c>
@@ -6021,7 +6029,7 @@
       <c r="A45" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="52">
         <f>B39*B40*B41*(1-B42)</f>
         <v>0.00011875</v>
       </c>
@@ -6042,7 +6050,7 @@
       <c r="A46" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="52">
         <f>B39*B40*B41*B42*(1-B43)</f>
         <v>5.9375e-6</v>
       </c>
@@ -6063,7 +6071,7 @@
       <c r="A47" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="52">
         <f>B39*B40*B41*B42*B43</f>
         <v>3.125e-7</v>
       </c>
@@ -6084,7 +6092,7 @@
       <c r="A48" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="53">
         <f>SUM(B45:B47)</f>
         <v>0.000125</v>
       </c>
@@ -6345,7 +6353,7 @@
       <c r="A61" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="52">
         <f>B56*B57*B58</f>
         <v>8e-6</v>
       </c>
@@ -6366,7 +6374,7 @@
       <c r="A62" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="53">
         <f>B61*B53</f>
         <v>0.00016</v>
       </c>
@@ -6568,7 +6576,7 @@
       <c r="A72" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="53">
         <f>B71/B70</f>
         <v>0.003</v>
       </c>
